--- a/exports/trend_1d/LODHA_full_report.xlsx
+++ b/exports/trend_1d/LODHA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:U37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>20.16</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44489</v>
+        <v>44490</v>
       </c>
       <c r="H2" t="n">
-        <v>525.9</v>
+        <v>513.55</v>
       </c>
       <c r="I2" t="n">
         <v>524.3908112696489</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K2" t="n">
-        <v>75.97</v>
+        <v>71.84</v>
       </c>
       <c r="L2" t="n">
         <v>2.51</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>20.36</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44509</v>
+        <v>44510</v>
       </c>
       <c r="H3" t="n">
-        <v>591.85</v>
+        <v>616.8</v>
       </c>
       <c r="I3" t="n">
         <v>603.8225523180465</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>-15.25</v>
+        <v>-20.11</v>
       </c>
       <c r="L3" t="n">
-        <v>18.78</v>
+        <v>20.73</v>
       </c>
       <c r="M3" t="n">
         <v>3.11</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>19.3</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44546</v>
+        <v>44547</v>
       </c>
       <c r="H4" t="n">
-        <v>631.45</v>
+        <v>592.05</v>
       </c>
       <c r="I4" t="n">
         <v>603.1730906232727</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K4" t="n">
-        <v>2.38</v>
+        <v>-4.01</v>
       </c>
       <c r="L4" t="n">
-        <v>5.64</v>
+        <v>5.77</v>
       </c>
       <c r="M4" t="n">
         <v>3.41</v>
       </c>
       <c r="N4" t="n">
-        <v>4.75</v>
+        <v>6.24</v>
       </c>
       <c r="O4" t="n">
         <v>4.22</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>24.01</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44593</v>
+        <v>44594</v>
       </c>
       <c r="H5" t="n">
-        <v>648.6</v>
+        <v>686.15</v>
       </c>
       <c r="I5" t="n">
         <v>680.8110997914695</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K5" t="n">
-        <v>-9.550000000000001</v>
+        <v>-15.89</v>
       </c>
       <c r="L5" t="n">
-        <v>12.97</v>
+        <v>17.56</v>
       </c>
       <c r="M5" t="n">
         <v>3.19</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>17.08</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H6" t="n">
-        <v>596.15</v>
+        <v>527.05</v>
       </c>
       <c r="I6" t="n">
         <v>569.5235513800069</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K6" t="n">
-        <v>-13.12</v>
+        <v>-23.19</v>
       </c>
       <c r="L6" t="n">
-        <v>14.64</v>
+        <v>25.31</v>
       </c>
       <c r="M6" t="n">
-        <v>4.44</v>
+        <v>7.66</v>
       </c>
       <c r="N6" t="n">
-        <v>6.54</v>
+        <v>11.59</v>
       </c>
       <c r="O6" t="n">
         <v>5.79</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>23.16</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44652</v>
+        <v>44655</v>
       </c>
       <c r="H7" t="n">
-        <v>590.25</v>
+        <v>600.7</v>
       </c>
       <c r="I7" t="n">
         <v>599.3597643666715</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K7" t="n">
-        <v>-11.99</v>
+        <v>-13.97</v>
       </c>
       <c r="L7" t="n">
-        <v>13.06</v>
+        <v>15.83</v>
       </c>
       <c r="M7" t="n">
         <v>4.36</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>11.59</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44669</v>
+        <v>44670</v>
       </c>
       <c r="H8" t="n">
-        <v>546.9</v>
+        <v>521.05</v>
       </c>
       <c r="I8" t="n">
         <v>531.0778085265025</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.960000000000001</v>
+        <v>-13.26</v>
       </c>
       <c r="L8" t="n">
-        <v>9.26</v>
+        <v>14.97</v>
       </c>
       <c r="M8" t="n">
         <v>1.93</v>
       </c>
       <c r="N8" t="n">
-        <v>3.78</v>
+        <v>4.73</v>
       </c>
       <c r="O8" t="n">
         <v>1.77</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>15.5</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44714</v>
+        <v>44715</v>
       </c>
       <c r="H9" t="n">
-        <v>517.45</v>
+        <v>545.55</v>
       </c>
       <c r="I9" t="n">
         <v>518.1121391042032</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6899999999999999</v>
+        <v>-4.7</v>
       </c>
       <c r="L9" t="n">
-        <v>5.56</v>
+        <v>5.75</v>
       </c>
       <c r="M9" t="n">
         <v>3.26</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>18.84</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44776</v>
+        <v>44777</v>
       </c>
       <c r="H10" t="n">
-        <v>552.4</v>
+        <v>518.6</v>
       </c>
       <c r="I10" t="n">
         <v>523.1283406588386</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K10" t="n">
-        <v>1.26</v>
+        <v>-4.94</v>
       </c>
       <c r="L10" t="n">
         <v>9.699999999999999</v>
@@ -1011,7 +1130,7 @@
         <v>2.58</v>
       </c>
       <c r="N10" t="n">
-        <v>3.73</v>
+        <v>6.12</v>
       </c>
       <c r="O10" t="n">
         <v>5.43</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>13.82</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44852</v>
+        <v>44853</v>
       </c>
       <c r="H11" t="n">
-        <v>504.75</v>
+        <v>514.8</v>
       </c>
       <c r="I11" t="n">
         <v>513.5146461835102</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K11" t="n">
-        <v>2.67</v>
+        <v>0.73</v>
       </c>
       <c r="L11" t="n">
         <v>11.26</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>13.56</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44959</v>
+        <v>44960</v>
       </c>
       <c r="H12" t="n">
-        <v>507.45</v>
+        <v>487.3</v>
       </c>
       <c r="I12" t="n">
         <v>497.6592314489517</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.43</v>
+        <v>-5.34</v>
       </c>
       <c r="L12" t="n">
         <v>10.35</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>15.15</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44986</v>
+        <v>44987</v>
       </c>
       <c r="H13" t="n">
-        <v>422.35</v>
+        <v>498.65</v>
       </c>
       <c r="I13" t="n">
         <v>444.0326840777848</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K13" t="n">
-        <v>13.33</v>
+        <v>-2.33</v>
       </c>
       <c r="L13" t="n">
         <v>5.07</v>
@@ -1182,7 +1337,7 @@
         <v>0.8</v>
       </c>
       <c r="N13" t="n">
-        <v>12.24</v>
+        <v>18.07</v>
       </c>
       <c r="O13" t="n">
         <v>-3.97</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>26.68</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45009</v>
+        <v>45012</v>
       </c>
       <c r="H14" t="n">
-        <v>413.05</v>
+        <v>397.7</v>
       </c>
       <c r="I14" t="n">
         <v>408.3532623789088</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K14" t="n">
-        <v>-17.17</v>
+        <v>-20.24</v>
       </c>
       <c r="L14" t="n">
-        <v>17.68</v>
+        <v>21.23</v>
       </c>
       <c r="M14" t="n">
         <v>2.76</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>18.52</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45022</v>
+        <v>45026</v>
       </c>
       <c r="H15" t="n">
-        <v>457.25</v>
+        <v>471.4</v>
       </c>
       <c r="I15" t="n">
         <v>469.7915057542288</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
-        <v>-14.97</v>
+        <v>-18.53</v>
       </c>
       <c r="L15" t="n">
         <v>19.56</v>
       </c>
       <c r="M15" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="N15" t="n">
         <v>9.98</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>17.49</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45162</v>
+        <v>45163</v>
       </c>
       <c r="H16" t="n">
-        <v>681.85</v>
+        <v>654.8</v>
       </c>
       <c r="I16" t="n">
         <v>673.8939957645709</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K16" t="n">
-        <v>44.64</v>
+        <v>38.91</v>
       </c>
       <c r="L16" t="n">
         <v>6.65</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>13.52</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45175</v>
+        <v>45176</v>
       </c>
       <c r="H17" t="n">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="I17" t="n">
         <v>735.9578460093409</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K17" t="n">
-        <v>-10.26</v>
+        <v>-13.47</v>
       </c>
       <c r="L17" t="n">
-        <v>12.87</v>
+        <v>13.93</v>
       </c>
       <c r="M17" t="n">
         <v>1.14</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>12.48</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45316</v>
+        <v>45320</v>
       </c>
       <c r="H18" t="n">
-        <v>1056.05</v>
+        <v>1034.25</v>
       </c>
       <c r="I18" t="n">
         <v>1049.043366192112</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K18" t="n">
-        <v>42.13</v>
+        <v>39.2</v>
       </c>
       <c r="L18" t="n">
         <v>5.56</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>18.92</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45391</v>
+        <v>45392</v>
       </c>
       <c r="H19" t="n">
-        <v>1200.05</v>
+        <v>1227.1</v>
       </c>
       <c r="I19" t="n">
         <v>1210.61816123321</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K19" t="n">
-        <v>-16.03</v>
+        <v>-18.65</v>
       </c>
       <c r="L19" t="n">
         <v>23.56</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>12.1</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45495</v>
+        <v>45496</v>
       </c>
       <c r="H20" t="n">
-        <v>1437.85</v>
+        <v>1369.9</v>
       </c>
       <c r="I20" t="n">
         <v>1391.416287029392</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K20" t="n">
-        <v>17.17</v>
+        <v>11.64</v>
       </c>
       <c r="L20" t="n">
         <v>11.34</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>19.12</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45554</v>
+        <v>45555</v>
       </c>
       <c r="H21" t="n">
-        <v>1303.5</v>
+        <v>1395.85</v>
       </c>
       <c r="I21" t="n">
         <v>1308.183996088145</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K21" t="n">
-        <v>4.85</v>
+        <v>-1.89</v>
       </c>
       <c r="L21" t="n">
         <v>6.87</v>
@@ -1638,7 +1889,7 @@
         <v>4.34</v>
       </c>
       <c r="N21" t="n">
-        <v>4.73</v>
+        <v>7.08</v>
       </c>
       <c r="O21" t="n">
         <v>-4.73</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>13.51</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45562</v>
+        <v>45565</v>
       </c>
       <c r="H22" t="n">
-        <v>1300.4</v>
+        <v>1234.4</v>
       </c>
       <c r="I22" t="n">
         <v>1256.549828182785</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.84</v>
+        <v>-11.57</v>
       </c>
       <c r="L22" t="n">
-        <v>8.24</v>
+        <v>12.31</v>
       </c>
       <c r="M22" t="n">
         <v>4.26</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>16.89</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45601</v>
+        <v>45602</v>
       </c>
       <c r="H23" t="n">
-        <v>1161.7</v>
+        <v>1218.55</v>
       </c>
       <c r="I23" t="n">
         <v>1215.688816327669</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K23" t="n">
-        <v>5.89</v>
+        <v>1.28</v>
       </c>
       <c r="L23" t="n">
         <v>4.42</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>15.99</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="H24" t="n">
-        <v>1350.35</v>
+        <v>1309.3</v>
       </c>
       <c r="I24" t="n">
         <v>1329.650185452162</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K24" t="n">
-        <v>10.82</v>
+        <v>7.45</v>
       </c>
       <c r="L24" t="n">
         <v>4.66</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>14</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="H25" t="n">
-        <v>1204.5</v>
+        <v>1280.15</v>
       </c>
       <c r="I25" t="n">
         <v>1252.87936275912</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K25" t="n">
-        <v>8</v>
+        <v>2.23</v>
       </c>
       <c r="L25" t="n">
         <v>3.54</v>
@@ -1866,7 +2165,7 @@
         <v>1.56</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>6.28</v>
       </c>
       <c r="O25" t="n">
         <v>-3.04</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>18.52</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H26" t="n">
-        <v>1113</v>
+        <v>1075.7</v>
       </c>
       <c r="I26" t="n">
         <v>1112.376005637661</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K26" t="n">
-        <v>-13.06</v>
+        <v>-15.97</v>
       </c>
       <c r="L26" t="n">
-        <v>15.08</v>
+        <v>16.26</v>
       </c>
       <c r="M26" t="n">
         <v>2.37</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,25 +2282,25 @@
         <v>15.84</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H27" t="n">
-        <v>1180.75</v>
+        <v>1216.75</v>
       </c>
       <c r="I27" t="n">
         <v>1207.315606630011</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
-        <v>-9.77</v>
+        <v>-13.11</v>
       </c>
       <c r="L27" t="n">
-        <v>15.1</v>
+        <v>15.27</v>
       </c>
       <c r="M27" t="n">
-        <v>0.53</v>
+        <v>0.78</v>
       </c>
       <c r="N27" t="n">
         <v>5.88</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>13.92</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45840</v>
+        <v>45841</v>
       </c>
       <c r="H28" t="n">
-        <v>1398.8</v>
+        <v>1368.9</v>
       </c>
       <c r="I28" t="n">
         <v>1379.158919630681</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K28" t="n">
-        <v>14.96</v>
+        <v>12.5</v>
       </c>
       <c r="L28" t="n">
         <v>11.57</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>10.51</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="H29" t="n">
-        <v>1171.4</v>
+        <v>1197.9</v>
       </c>
       <c r="I29" t="n">
         <v>1196.35734586596</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K29" t="n">
-        <v>14.43</v>
+        <v>12.49</v>
       </c>
       <c r="L29" t="n">
         <v>6.76</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>5</v>
+      </c>
+      <c r="U29" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>6.68</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="H30" t="n">
-        <v>1148.2</v>
+        <v>1128.2</v>
       </c>
       <c r="I30" t="n">
         <v>1147.369207412446</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.15</v>
+        <v>-5.82</v>
       </c>
       <c r="L30" t="n">
-        <v>4.39</v>
+        <v>6.08</v>
       </c>
       <c r="M30" t="n">
         <v>0.37</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H31" t="n">
-        <v>961.45</v>
+        <v>1031.9</v>
       </c>
       <c r="I31" t="n">
         <v>1004.702954698851</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K31" t="n">
-        <v>14.78</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="L31" t="n">
         <v>2.64</v>
@@ -2208,7 +2579,7 @@
         <v>4.24</v>
       </c>
       <c r="N31" t="n">
-        <v>4.77</v>
+        <v>7.33</v>
       </c>
       <c r="O31" t="n">
         <v>-1.74</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>15.97</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="H32" t="n">
-        <v>1011.5</v>
+        <v>988.25</v>
       </c>
       <c r="I32" t="n">
         <v>995.6813083746159</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.98</v>
+        <v>-4.23</v>
       </c>
       <c r="L32" t="n">
         <v>4.59</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>11.85</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="H33" t="n">
-        <v>778.85</v>
+        <v>789.55</v>
       </c>
       <c r="I33" t="n">
         <v>787.9569395929052</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K33" t="n">
-        <v>21.19</v>
+        <v>20.11</v>
       </c>
       <c r="L33" t="n">
         <v>2.5</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>15.56</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="H34" t="n">
-        <v>872.85</v>
+        <v>849.95</v>
       </c>
       <c r="I34" t="n">
         <v>868.0016783402139</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K34" t="n">
-        <v>10.55</v>
+        <v>7.65</v>
       </c>
       <c r="L34" t="n">
         <v>3.44</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>13.4</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="H35" t="n">
-        <v>937.85</v>
+        <v>947.45</v>
       </c>
       <c r="I35" t="n">
         <v>946.2945570361985</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K35" t="n">
-        <v>-10.34</v>
+        <v>-11.47</v>
       </c>
       <c r="L35" t="n">
-        <v>14.01</v>
+        <v>14.36</v>
       </c>
       <c r="M35" t="n">
         <v>2.25</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>9.18</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="H36" t="n">
-        <v>1212</v>
+        <v>1166</v>
       </c>
       <c r="I36" t="n">
         <v>1173.81978302084</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K36" t="n">
-        <v>27.92</v>
+        <v>23.07</v>
       </c>
       <c r="L36" t="n">
         <v>1.74</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2553,6 +2996,14 @@
       <c r="Q37" t="n">
         <v>33</v>
       </c>
+      <c r="R37" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4961,7 +5412,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54.3</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="6">
@@ -4971,7 +5422,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -4981,7 +5432,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8">
@@ -4991,7 +5442,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -5001,7 +5452,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
@@ -5011,7 +5462,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>113.8</v>
+        <v>114.8</v>
       </c>
     </row>
     <row r="11">
@@ -5021,7 +5472,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -5031,7 +5482,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -5041,7 +5492,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.3</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="14">
@@ -5051,7 +5502,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.82</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="15">
@@ -5061,7 +5512,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10.06</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="16">
@@ -5071,7 +5522,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.73</v>
+        <v>-5.22</v>
       </c>
     </row>
     <row r="17">
@@ -5081,7 +5532,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>75.97</v>
+        <v>71.84</v>
       </c>
     </row>
     <row r="18">
@@ -5091,7 +5542,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -5101,7 +5552,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.300000000000001</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="20">
@@ -5111,7 +5562,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8.24</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -5121,7 +5572,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23.56</v>
+        <v>25.31</v>
       </c>
     </row>
     <row r="22">
@@ -5131,7 +5582,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
@@ -5141,7 +5592,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -5151,7 +5602,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.91</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="25">
@@ -5161,7 +5612,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.45</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="26">
@@ -5171,7 +5622,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6.16</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="27">
@@ -5181,7 +5632,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.24</v>
+        <v>18.07</v>
       </c>
     </row>
     <row r="28">
@@ -5191,7 +5642,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
